--- a/files/九龙-旺角-Upper Prince.xlsx
+++ b/files/九龙-旺角-Upper Prince.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upper Prince 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -6852,7 +6719,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6948,7 +6815,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -7620,1426 +7487,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Upper Prince - Upper Prince 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>139 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>137 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 487呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 357呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 265呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 215呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 265呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 215呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 265呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 215呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 265呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 215呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-$515万
-$20,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 265呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 215呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 347呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 248呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 259呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 271呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 265呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 215呎 (开放式)
-$442万
-$20,563/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 324呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 228呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 238呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 250呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 245呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 278呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 192呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-旺角-Upper Prince.xlsx
+++ b/files/九龙-旺角-Upper Prince.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upper Prince" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +136,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +217,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7487,4 +7657,1426 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Upper Prince 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 487呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 357呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 265呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 215呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 265呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 215呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 265呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 215呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 265呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 215呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+$515万
+$20,750/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 265呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 215呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 347呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 248呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 259呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 271呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 265呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 215呎 (开放式)
+$442万
+$20,563/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 324呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 228呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 238呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 250呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 245呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 278呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 192呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-旺角-Upper Prince.xlsx
+++ b/files/九龙-旺角-Upper Prince.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:N141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -704,6 +708,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -754,6 +778,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -804,6 +848,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -854,6 +918,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -904,6 +988,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -954,6 +1058,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1004,6 +1128,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1054,6 +1198,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1104,6 +1268,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1154,6 +1338,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1204,6 +1408,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1254,6 +1478,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1304,6 +1548,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1354,6 +1618,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1404,6 +1688,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1454,6 +1758,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1504,6 +1828,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1554,6 +1898,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1604,6 +1968,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1654,6 +2038,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1704,6 +2108,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1754,6 +2178,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1804,6 +2248,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1854,6 +2318,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1904,6 +2388,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1954,6 +2458,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2004,6 +2528,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2054,6 +2598,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2104,6 +2668,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2154,6 +2738,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2204,6 +2808,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2254,6 +2878,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2304,6 +2948,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2354,6 +3018,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2404,6 +3088,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2454,6 +3158,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2504,6 +3228,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2554,6 +3298,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2604,6 +3368,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2654,6 +3438,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2704,6 +3508,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2754,6 +3578,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2804,6 +3648,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2854,6 +3718,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2904,6 +3788,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2954,6 +3858,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3004,6 +3928,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3054,6 +3998,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3104,6 +4068,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3154,6 +4138,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3204,6 +4208,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3254,6 +4278,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3304,6 +4348,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3354,6 +4418,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3404,6 +4488,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3454,6 +4558,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3504,6 +4628,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3554,6 +4698,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3604,6 +4768,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3654,6 +4838,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3704,6 +4908,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3754,6 +4978,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3804,6 +5048,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3854,6 +5118,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3904,6 +5188,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3954,6 +5258,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4004,6 +5328,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4054,6 +5398,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4104,6 +5468,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4154,6 +5538,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4204,6 +5608,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4254,6 +5678,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4304,6 +5748,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4354,6 +5818,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4404,6 +5888,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4454,6 +5958,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4504,6 +6028,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4554,6 +6098,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4604,6 +6168,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4654,6 +6238,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4704,6 +6308,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4754,6 +6378,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4804,6 +6448,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4854,6 +6518,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4904,6 +6588,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4954,6 +6658,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5004,6 +6728,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5054,6 +6798,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5104,6 +6868,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5154,6 +6938,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5204,6 +7008,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5254,6 +7078,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5304,6 +7148,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5354,6 +7218,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5404,6 +7288,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5454,6 +7358,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5504,6 +7428,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5554,6 +7498,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5604,6 +7568,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5654,6 +7638,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5704,6 +7708,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5754,6 +7778,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5804,6 +7848,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5854,6 +7918,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5904,6 +7988,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5954,6 +8058,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6004,6 +8128,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6054,6 +8198,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6104,6 +8268,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6154,6 +8338,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6204,6 +8408,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6254,6 +8478,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6304,6 +8548,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6354,6 +8618,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6404,6 +8688,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6454,6 +8758,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6504,6 +8828,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6554,6 +8898,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6604,6 +8968,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6654,6 +9038,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6704,6 +9108,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6754,6 +9178,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6804,6 +9248,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6854,6 +9318,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6900,6 +9384,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6950,6 +9454,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6996,6 +9520,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7046,6 +9590,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7096,6 +9660,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7146,6 +9730,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7196,6 +9800,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7246,6 +9870,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7296,6 +9940,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7346,6 +10010,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7396,6 +10080,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7446,6 +10150,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7496,6 +10220,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7546,6 +10290,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7596,6 +10360,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7646,13 +10430,33 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8902,7 +11706,7 @@
           <t>B | 248呎 (1房)
 $515万
 $20,750/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9005,7 +11809,7 @@
           <t>G | 215呎 (开放式)
 $442万
 $20,563/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
     </row>
